--- a/artfynd/A 56389-2019 artfynd.xlsx
+++ b/artfynd/A 56389-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125814666</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56389-2019 artfynd.xlsx
+++ b/artfynd/A 56389-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125814666</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56389-2019 artfynd.xlsx
+++ b/artfynd/A 56389-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125814666</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
